--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N14" t="n">
-        <v>2.36</v>
+        <v>2.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,22 +13146,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G128" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N64" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G125" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,16 +1510,16 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M44" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="M109" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N109" t="n">
-        <v>6.5</v>
+        <v>7.6</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15150,16 +15150,16 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G123" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK128"/>
+  <dimension ref="A1:AK129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="18">
@@ -2697,22 +2697,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5788,27 +5788,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="44">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="48">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N71" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="73">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="89">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13141,27 +13141,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="100">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M109" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15150,16 +15150,16 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15334,27 +15334,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="117">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45919.67708333334</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45919.79166666666</v>
+        <v>45919.67708333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,12 +15979,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.79166666666</v>
       </c>
     </row>
     <row r="122">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="125">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="127">
@@ -16753,12 +16753,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45919.95833333334</v>
+        <v>45919.89583333334</v>
       </c>
     </row>
     <row r="128">
@@ -16887,121 +16887,250 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" s="3" t="n">
+        <v>45919.95833333334</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" s="3" t="n">
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="M62" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N62" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,22 +13275,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,22 +13404,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK129"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1402,27 +1402,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1439,65 +1439,65 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,19 +1510,19 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.375</v>
       </c>
     </row>
     <row r="9">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="13">
@@ -2047,27 +2047,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2434,27 +2434,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.51041666666</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45919.51041666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="31">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,22 +5277,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N45" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N47" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.59375</v>
       </c>
     </row>
     <row r="62">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,22 +8760,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M67" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N67" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S69" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U69" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V69" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W69" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X69" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA69" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB69" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC69" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="91">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13270,12 +13270,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.75</v>
+        <v>1.53</v>
       </c>
       <c r="M100" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N100" t="n">
-        <v>2.8</v>
+        <v>5.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13344,16 +13344,16 @@
         <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.66</v>
+        <v>2.1</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15463,12 +15463,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="119">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45919.67708333334</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="121">
@@ -15979,27 +15979,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45919.79166666666</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,27 +16108,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.67708333334</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.6875</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.79166666666</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -16753,7 +16753,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
       <c r="AK127" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="128">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45919.95833333334</v>
+        <v>45919.85416666666</v>
       </c>
     </row>
     <row r="129">
@@ -17011,126 +17011,642 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Houston Dash</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" s="3" t="n">
+        <v>45919.875</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Orlando Pride</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>North Carolina Courage</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK130" s="3" t="n">
+        <v>45919.875</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK131" s="3" t="n">
+        <v>45919.89583333334</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0</v>
-      </c>
-      <c r="N129" t="n">
-        <v>0</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" s="3" t="n">
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="3" t="n">
+        <v>45919.95833333334</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45919.41666666666</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5100,10 +5100,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.59</v>
+        <v>1.94</v>
       </c>
       <c r="M56" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N56" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="M58" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="N58" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M64" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N64" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,61 +9312,61 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P69" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T69" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U69" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W69" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB69" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC69" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE69" t="inlineStr">
         <is>
@@ -9379,10 +9379,10 @@
         </is>
       </c>
       <c r="AG69" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.92</v>
+        <v>3.85</v>
       </c>
       <c r="M70" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.93</v>
+        <v>2.8</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9831,58 +9831,58 @@
         <v>2.8</v>
       </c>
       <c r="M73" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N73" t="n">
         <v>2.55</v>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S73" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T73" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U73" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V73" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W73" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X73" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB73" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC73" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD73" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH73" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.75</v>
+        <v>1.4</v>
       </c>
       <c r="M105" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="N105" t="n">
-        <v>2.8</v>
+        <v>7.6</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13989,16 +13989,16 @@
         <v>0</v>
       </c>
       <c r="W105" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.23</v>
+        <v>1.67</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15150,16 +15150,16 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X114" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16500,7 +16500,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G127" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AK132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>4.05</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,22 +5019,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,16 +5094,16 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="M62" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="M63" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N63" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="M68" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9573,58 +9573,58 @@
         <v>2.8</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N71" t="n">
         <v>2.55</v>
       </c>
       <c r="O71" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S71" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U71" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V71" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W71" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X71" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB71" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC71" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,65 +9824,65 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P73" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U73" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W73" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X73" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB73" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC73" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD73" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE73" t="inlineStr">
         <is>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="AG73" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.7</v>
+        <v>1.22</v>
       </c>
       <c r="M77" t="n">
-        <v>3.9</v>
+        <v>6.3</v>
       </c>
       <c r="N77" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,16 +10383,16 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11550,10 +11550,10 @@
         <v>0</v>
       </c>
       <c r="AA86" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB86" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.73</v>
+        <v>6.8</v>
       </c>
       <c r="M104" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="N104" t="n">
-        <v>4.8</v>
+        <v>1.5</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.75</v>
+        <v>1.73</v>
       </c>
       <c r="M114" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N114" t="n">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15150,16 +15150,16 @@
         <v>0</v>
       </c>
       <c r="W114" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45919.85416666666</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="129">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.89583333334</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.95833333334</v>
       </c>
     </row>
     <row r="132">
@@ -17518,135 +17518,6 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45919.95833333334</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK132"/>
+  <dimension ref="A1:AK133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1407,22 +1407,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1923,22 +1923,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2052,22 +2052,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4842,10 +4842,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.99</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.6</v>
+        <v>5.83</v>
       </c>
       <c r="M37" t="n">
-        <v>3.7</v>
+        <v>4.47</v>
       </c>
       <c r="N37" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,22 +5406,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8025,10 +8025,10 @@
         <v>1.53</v>
       </c>
       <c r="M59" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N59" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="M60" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N60" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.93</v>
+        <v>2.65</v>
       </c>
       <c r="M66" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9573,58 +9573,58 @@
         <v>2.8</v>
       </c>
       <c r="M71" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
         <v>2.55</v>
       </c>
       <c r="O71" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T71" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U71" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V71" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W71" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X71" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB71" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC71" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE71" t="inlineStr">
         <is>
@@ -9637,10 +9637,10 @@
         </is>
       </c>
       <c r="AG71" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10389,10 +10389,10 @@
         <v>0</v>
       </c>
       <c r="AA77" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB77" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,22 +13662,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M105" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.75</v>
+        <v>1.85</v>
       </c>
       <c r="M107" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.23</v>
+        <v>1.75</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M108" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N108" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z108" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M109" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Z109" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>3.95</v>
       </c>
       <c r="N110" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M111" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M116" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N116" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z116" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M118" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N118" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.85416666666</v>
       </c>
     </row>
     <row r="129">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45919.95833333334</v>
+        <v>45919.89583333334</v>
       </c>
     </row>
     <row r="132">
@@ -17403,121 +17403,250 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" s="3" t="n">
+        <v>45919.95833333334</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="inlineStr">
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" s="3" t="n">
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1794,22 +1794,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,16 +1897,16 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45919.41666666666</v>
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,22 +2439,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.17</v>
+        <v>1.76</v>
       </c>
       <c r="M35" t="n">
-        <v>3.8</v>
+        <v>3.89</v>
       </c>
       <c r="N35" t="n">
-        <v>2.65</v>
+        <v>3.59</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4971,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>5.83</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>4.47</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5.83</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>4.47</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6519,10 +6519,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="M63" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="M64" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N64" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="O64" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U64" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V64" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X64" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA64" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N65" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.65</v>
+        <v>3.85</v>
       </c>
       <c r="M66" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N66" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,61 +9183,61 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="M68" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N68" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O68" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,10 +9570,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="N71" t="n">
         <v>2.55</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M72" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N72" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N73" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N74" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="M80" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N80" t="n">
-        <v>2.55</v>
+        <v>4.8</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z80" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.53</v>
+        <v>2.49</v>
       </c>
       <c r="M97" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="N97" t="n">
-        <v>5.4</v>
+        <v>2.6</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M104" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="M105" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N105" t="n">
-        <v>1.77</v>
+        <v>4.5</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="M106" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N106" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14118,16 +14118,16 @@
         <v>0</v>
       </c>
       <c r="W106" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M107" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N107" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.7</v>
+        <v>2.75</v>
       </c>
       <c r="M109" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N109" t="n">
-        <v>4.2</v>
+        <v>2.8</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X109" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="M110" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="N110" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="M111" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N111" t="n">
-        <v>7.6</v>
+        <v>4.8</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.35</v>
+        <v>1.45</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="N116" t="n">
-        <v>3.15</v>
+        <v>6.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M117" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45919.375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1789,27 +1789,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1826,65 +1826,65 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,19 +1897,19 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="12">
@@ -1918,27 +1918,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2038,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="AK12" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="14">
@@ -2181,22 +2181,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="20">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4111,12 +4111,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
       <c r="AK29" s="3" t="n">
-        <v>45919.51041666666</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="30">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.51041666666</v>
       </c>
     </row>
     <row r="32">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45919.52430555555</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52430555555</v>
       </c>
     </row>
     <row r="36">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.83</v>
+        <v>2.6</v>
       </c>
       <c r="M36" t="n">
-        <v>4.47</v>
+        <v>3.7</v>
       </c>
       <c r="N36" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,22 +5535,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.17</v>
+        <v>5.83</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>4.47</v>
       </c>
       <c r="N40" t="n">
-        <v>2.65</v>
+        <v>1.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="45">
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6390,10 +6390,10 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="49">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,10 +6894,10 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M52" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7152,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45919.59375</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.59375</v>
       </c>
     </row>
     <row r="63">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,49 +8538,49 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="N63" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="n">
         <v>2.2</v>
       </c>
-      <c r="O63" t="n">
-        <v>0</v>
-      </c>
-      <c r="P63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0</v>
-      </c>
-      <c r="T63" t="n">
-        <v>0</v>
-      </c>
-      <c r="U63" t="n">
-        <v>0</v>
-      </c>
-      <c r="V63" t="n">
-        <v>0</v>
-      </c>
-      <c r="W63" t="n">
-        <v>0</v>
-      </c>
-      <c r="X63" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Z63" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="M64" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N64" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M65" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="N65" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.85</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,22 +9018,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,65 +9179,65 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P68" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="inlineStr">
         <is>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="AG68" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9308,17 +9308,17 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M71" t="n">
         <v>3</v>
       </c>
       <c r="N71" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.1</v>
+        <v>2.85</v>
       </c>
       <c r="M72" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10131,10 +10131,10 @@
         <v>0</v>
       </c>
       <c r="AA75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10260,10 +10260,10 @@
         <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="M99" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z99" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="M102" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N102" t="n">
-        <v>1.77</v>
+        <v>3.15</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="Z102" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13731,16 +13731,16 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="M104" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="N104" t="n">
-        <v>7.6</v>
+        <v>1.77</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="M109" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N109" t="n">
-        <v>2.8</v>
+        <v>4.05</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14505,16 +14505,16 @@
         <v>0</v>
       </c>
       <c r="W109" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.23</v>
+        <v>1.77</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="M111" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="N111" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="M112" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N112" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M116" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="N116" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.35</v>
+        <v>1.73</v>
       </c>
       <c r="M118" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N118" t="n">
-        <v>3.15</v>
+        <v>4.8</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK133"/>
+  <dimension ref="A1:AK135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>2.7</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="19">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="20">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,13 +4023,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4062,10 +4062,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45919.51041666666</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.51041666666</v>
       </c>
     </row>
     <row r="34">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45919.52430555555</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="37">
@@ -5143,27 +5143,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5229,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52430555555</v>
       </c>
     </row>
     <row r="38">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="M38" t="n">
-        <v>3.89</v>
+        <v>3.34</v>
       </c>
       <c r="N38" t="n">
-        <v>3.59</v>
+        <v>3.17</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>5.83</v>
+        <v>2.42</v>
       </c>
       <c r="M40" t="n">
-        <v>4.47</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="N41" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.99</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6046,12 +6046,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.7</v>
+        <v>2.17</v>
       </c>
       <c r="M45" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4.1</v>
+        <v>2.65</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="47">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.53</v>
+        <v>2.12</v>
       </c>
       <c r="M49" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="N49" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="50">
@@ -6820,27 +6820,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="51">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7023,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7152,10 +7152,10 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45919.59375</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.59375</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="M65" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M67" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N67" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N69" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="M71" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="N71" t="n">
-        <v>2.7</v>
+        <v>2.39</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.85</v>
+        <v>1.92</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>2.55</v>
+        <v>3.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L73" t="n">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.22</v>
+        <v>2.1</v>
       </c>
       <c r="M76" t="n">
-        <v>6.3</v>
+        <v>3.2</v>
       </c>
       <c r="N76" t="n">
-        <v>9.5</v>
+        <v>3.4</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10776,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="M82" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N82" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="N83" t="n">
-        <v>4.8</v>
+        <v>3.57</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="93">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13528,27 +13528,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -13657,12 +13657,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,10 +13698,10 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.64</v>
+        <v>2.06</v>
       </c>
       <c r="M103" t="n">
-        <v>2.89</v>
+        <v>3.45</v>
       </c>
       <c r="N103" t="n">
         <v>2.9</v>
@@ -13731,16 +13731,16 @@
         <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>4</v>
+        <v>1.45</v>
       </c>
       <c r="M104" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="N104" t="n">
-        <v>1.77</v>
+        <v>6.7</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="M105" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="N105" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,49 +14085,49 @@
         </is>
       </c>
       <c r="L106" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M106" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N106" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+      <c r="S106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
+        <v>0</v>
+      </c>
+      <c r="U106" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" t="n">
+        <v>0</v>
+      </c>
+      <c r="W106" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z106" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M106" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N106" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O106" t="n">
-        <v>0</v>
-      </c>
-      <c r="P106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
-      <c r="R106" t="n">
-        <v>0</v>
-      </c>
-      <c r="S106" t="n">
-        <v>0</v>
-      </c>
-      <c r="T106" t="n">
-        <v>0</v>
-      </c>
-      <c r="U106" t="n">
-        <v>0</v>
-      </c>
-      <c r="V106" t="n">
-        <v>0</v>
-      </c>
-      <c r="W106" t="n">
-        <v>0</v>
-      </c>
-      <c r="X106" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y106" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Z106" t="n">
-        <v>1.84</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M107" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N107" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.7</v>
+        <v>6.8</v>
       </c>
       <c r="M109" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N109" t="n">
-        <v>4.05</v>
+        <v>1.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.45</v>
+        <v>4</v>
       </c>
       <c r="M111" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N111" t="n">
-        <v>6.7</v>
+        <v>1.77</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.08</v>
+        <v>1.73</v>
       </c>
       <c r="M112" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N112" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,14 +14988,14 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>6.8</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N113" t="n">
         <v>4.2</v>
       </c>
-      <c r="N113" t="n">
-        <v>1.5</v>
-      </c>
       <c r="O113" t="n">
         <v>0</v>
       </c>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15279,16 +15279,16 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X115" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="M116" t="n">
-        <v>4.9</v>
+        <v>3.95</v>
       </c>
       <c r="N116" t="n">
-        <v>7.6</v>
+        <v>4.5</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,7 +15414,7 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z116" t="n">
         <v>2.2</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M117" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,14 +15633,14 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="M118" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N118" t="n">
         <v>3.75</v>
       </c>
-      <c r="N118" t="n">
-        <v>4.8</v>
-      </c>
       <c r="O118" t="n">
         <v>0</v>
       </c>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z118" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z118" t="n">
-        <v>1.85</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="M119" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N119" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15804,7 +15804,7 @@
         <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="120">
@@ -15850,12 +15850,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="121">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16108,12 +16108,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45919.67708333334</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="123">
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45919.6875</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="124">
@@ -16366,27 +16366,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45919.79166666666</v>
+        <v>45919.67708333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,27 +16495,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.6875</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.79166666666</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16882,12 +16882,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17002,7 +17002,7 @@
         <v>0</v>
       </c>
       <c r="AK128" s="3" t="n">
-        <v>45919.85416666666</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="129">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M130" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.85416666666</v>
       </c>
     </row>
     <row r="131">
@@ -17269,12 +17269,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17389,7 +17389,7 @@
         <v>0</v>
       </c>
       <c r="AK131" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="132">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45919.95833333334</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="133">
@@ -17527,126 +17527,384 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Austin II</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>St. Louis City II</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" s="3" t="n">
+        <v>45919.89583333334</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Utah Royals</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Racing Louisville</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" s="3" t="n">
+        <v>45919.95833333334</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>45919</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
         <is>
           <t>USA MLS Next Pro</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>Los Angeles II</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>Real Monarchs</t>
         </is>
       </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3" t="n">
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -1020,22 +1020,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="M5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.375</v>
       </c>
     </row>
     <row r="9">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.47916666666</v>
       </c>
     </row>
     <row r="19">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="21">
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4152,61 +4152,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.17</v>
+        <v>1.48</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="N39" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>1.48</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6180,22 +6180,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.17</v>
+        <v>1.75</v>
       </c>
       <c r="M45" t="n">
         <v>3.8</v>
       </c>
       <c r="N45" t="n">
-        <v>2.65</v>
+        <v>3.51</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.7</v>
+        <v>2.12</v>
       </c>
       <c r="M47" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N47" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.12</v>
+        <v>1.7</v>
       </c>
       <c r="M49" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7023,10 +7023,10 @@
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="M54" t="n">
-        <v>3.51</v>
+        <v>4.1</v>
       </c>
       <c r="N54" t="n">
-        <v>3.63</v>
+        <v>4.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8325,10 +8325,10 @@
         <v>0</v>
       </c>
       <c r="AA61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N66" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M69" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N69" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.63</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>3.11</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>2.39</v>
+        <v>3.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9824,17 +9824,17 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="M76" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N76" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10776,10 +10776,10 @@
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB80" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.6</v>
+        <v>2.67</v>
       </c>
       <c r="M81" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>4.8</v>
+        <v>2.52</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>3.57</v>
+        <v>4.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="M85" t="n">
-        <v>3.28</v>
+        <v>6.3</v>
       </c>
       <c r="N85" t="n">
-        <v>3.3</v>
+        <v>9.5</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,16 +11415,16 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB85" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="M92" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N92" t="n">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="M95" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N95" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.35</v>
+        <v>1.67</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.64</v>
+        <v>2.06</v>
       </c>
       <c r="M98" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="Z98" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="M104" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="N104" t="n">
-        <v>6.7</v>
+        <v>4.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.98</v>
+        <v>6.8</v>
       </c>
       <c r="M107" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N107" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,14 +14472,14 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>6.8</v>
+        <v>1.98</v>
       </c>
       <c r="M109" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N109" t="n">
         <v>4.2</v>
       </c>
-      <c r="N109" t="n">
-        <v>1.5</v>
-      </c>
       <c r="O109" t="n">
         <v>0</v>
       </c>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>4</v>
+        <v>2.35</v>
       </c>
       <c r="M111" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>1.77</v>
+        <v>3.15</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="Z111" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.73</v>
+        <v>2.64</v>
       </c>
       <c r="M112" t="n">
-        <v>3.75</v>
+        <v>2.89</v>
       </c>
       <c r="N112" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X112" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>1.32</v>
       </c>
       <c r="M113" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="N113" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="M115" t="n">
-        <v>2.89</v>
+        <v>3.35</v>
       </c>
       <c r="N115" t="n">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15279,16 +15279,16 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X115" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.23</v>
+        <v>2</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="M117" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="N117" t="n">
-        <v>4.05</v>
+        <v>1.77</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="M118" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N118" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="M119" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="N119" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="M120" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="N120" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,7 +16059,7 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z121" t="n">
         <v>1.8</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Z123" t="n">
         <v>1.8</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N129" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4.05</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4.05</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>1.98</v>
       </c>
       <c r="M15" t="n">
         <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>3.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,13 +3120,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>5</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>4.1</v>
+        <v>3.29</v>
       </c>
       <c r="N38" t="n">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>3.64</v>
+        <v>2.11</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.42</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>3.51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N42" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5874,10 +5874,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>1.48</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="M45" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="N45" t="n">
-        <v>3.51</v>
+        <v>3.17</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="N49" t="n">
-        <v>4.1</v>
+        <v>3.81</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7281,10 +7281,10 @@
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z60" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,22 +8502,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="M63" t="n">
-        <v>3.51</v>
+        <v>4</v>
       </c>
       <c r="N63" t="n">
-        <v>3.63</v>
+        <v>4.15</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M66" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N66" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.55</v>
+        <v>2.63</v>
       </c>
       <c r="M70" t="n">
-        <v>3.21</v>
+        <v>3.11</v>
       </c>
       <c r="N70" t="n">
-        <v>1.9</v>
+        <v>2.39</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>1.92</v>
+        <v>2.65</v>
       </c>
       <c r="M72" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.65</v>
+        <v>1.93</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9953,17 +9953,17 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10211,17 +10211,17 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="M81" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N81" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M83" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z83" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11421,10 +11421,10 @@
         <v>0</v>
       </c>
       <c r="AA85" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB85" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11679,10 +11679,10 @@
         <v>0</v>
       </c>
       <c r="AA87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="M88" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="N88" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,49 +12021,49 @@
         </is>
       </c>
       <c r="L90" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M90" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="N90" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0</v>
+      </c>
+      <c r="S90" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" t="n">
+        <v>0</v>
+      </c>
+      <c r="U90" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" t="n">
+        <v>0</v>
+      </c>
+      <c r="W90" t="n">
+        <v>0</v>
+      </c>
+      <c r="X90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z90" t="n">
         <v>1.77</v>
-      </c>
-      <c r="M90" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N90" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0</v>
-      </c>
-      <c r="S90" t="n">
-        <v>0</v>
-      </c>
-      <c r="T90" t="n">
-        <v>0</v>
-      </c>
-      <c r="U90" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" t="n">
-        <v>0</v>
-      </c>
-      <c r="W90" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M96" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N96" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="M104" t="n">
         <v>3.6</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.8</v>
+        <v>1.32</v>
       </c>
       <c r="M105" t="n">
-        <v>4.05</v>
+        <v>5.2</v>
       </c>
       <c r="N105" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>6.8</v>
+        <v>2.64</v>
       </c>
       <c r="M107" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="N107" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N108" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.98</v>
+        <v>6.8</v>
       </c>
       <c r="M109" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N109" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="M110" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N110" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N111" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.64</v>
+        <v>1.71</v>
       </c>
       <c r="M112" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="N112" t="n">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14892,16 +14892,16 @@
         <v>0</v>
       </c>
       <c r="W112" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2.23</v>
+        <v>1.62</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="M113" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="N113" t="n">
-        <v>8.4</v>
+        <v>6.7</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15378,10 +15378,10 @@
         <v>1.65</v>
       </c>
       <c r="M116" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="N116" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="M117" t="n">
         <v>3.75</v>
       </c>
       <c r="N117" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M118" t="n">
         <v>3.7</v>
       </c>
       <c r="N118" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="M119" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="N119" t="n">
-        <v>3.75</v>
+        <v>1.77</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="M120" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N120" t="n">
-        <v>6.7</v>
+        <v>4.05</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M121" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="M127" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N127" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1665,22 +1665,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,16 +1768,16 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45919.41666666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,61 +3894,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
@@ -3961,10 +3961,10 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="M38" t="n">
-        <v>3.29</v>
+        <v>3.8</v>
       </c>
       <c r="N38" t="n">
-        <v>3.64</v>
+        <v>3.51</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,16 +5352,16 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>2.11</v>
+        <v>3.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>3.29</v>
       </c>
       <c r="N40" t="n">
-        <v>3.51</v>
+        <v>3.64</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="N42" t="n">
-        <v>3</v>
+        <v>2.11</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N43" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.42</v>
+        <v>5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.47</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M45" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,10 +6513,10 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,16 +6771,16 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,22 +7986,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X59" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -8115,22 +8115,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8313,10 +8313,10 @@
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y61" t="n">
         <v>0</v>
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="M70" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N70" t="n">
-        <v>2.39</v>
+        <v>2.7</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N71" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.93</v>
+        <v>2.85</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N73" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N74" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.85</v>
+        <v>1.93</v>
       </c>
       <c r="M75" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="N75" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N78" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.67</v>
+        <v>1.83</v>
       </c>
       <c r="M79" t="n">
         <v>3.35</v>
       </c>
       <c r="N79" t="n">
-        <v>2.52</v>
+        <v>3.63</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.95</v>
+        <v>1.77</v>
       </c>
       <c r="M81" t="n">
-        <v>3.28</v>
+        <v>3.61</v>
       </c>
       <c r="N81" t="n">
-        <v>3.3</v>
+        <v>3.59</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N82" t="n">
-        <v>3.63</v>
+        <v>2.91</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.22</v>
+        <v>4.4</v>
       </c>
       <c r="M87" t="n">
-        <v>6.3</v>
+        <v>3.8</v>
       </c>
       <c r="N87" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,16 +11673,16 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA87" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB87" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.25</v>
+        <v>1.22</v>
       </c>
       <c r="M91" t="n">
-        <v>3.45</v>
+        <v>6.3</v>
       </c>
       <c r="N91" t="n">
-        <v>3.1</v>
+        <v>9.5</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.24</v>
+        <v>1.6</v>
       </c>
       <c r="M92" t="n">
-        <v>3.03</v>
+        <v>4.1</v>
       </c>
       <c r="N92" t="n">
-        <v>2.91</v>
+        <v>4.8</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Z92" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="M99" t="n">
-        <v>3.35</v>
+        <v>3.37</v>
       </c>
       <c r="N99" t="n">
-        <v>4.4</v>
+        <v>2.54</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N101" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="M102" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N102" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="M104" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
       <c r="N104" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,22 +13920,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="M105" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="N105" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>2.64</v>
+        <v>6.8</v>
       </c>
       <c r="M107" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="N107" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14247,16 +14247,16 @@
         <v>0</v>
       </c>
       <c r="W107" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M108" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>6.8</v>
+        <v>1.71</v>
       </c>
       <c r="M109" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N109" t="n">
-        <v>1.5</v>
+        <v>3.89</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Z109" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N110" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="M111" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N111" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="M112" t="n">
         <v>3.6</v>
       </c>
       <c r="N112" t="n">
-        <v>3.89</v>
+        <v>3.75</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Z112" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.45</v>
+        <v>1.73</v>
       </c>
       <c r="M113" t="n">
-        <v>4.7</v>
+        <v>3.75</v>
       </c>
       <c r="N113" t="n">
-        <v>6.7</v>
+        <v>4.8</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="M114" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N114" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="M116" t="n">
-        <v>3.7</v>
+        <v>4.7</v>
       </c>
       <c r="N116" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.73</v>
+        <v>2.35</v>
       </c>
       <c r="M117" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="N117" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M118" t="n">
         <v>3.7</v>
       </c>
       <c r="N118" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15855,22 +15855,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="M120" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N120" t="n">
-        <v>4.05</v>
+        <v>4.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Z122" t="n">
         <v>1.8</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z123" t="n">
         <v>1.8</v>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N127" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M128" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z128" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>6.5</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,10 +4320,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -4374,22 +4374,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3.51</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5358,10 +5358,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.17</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.85</v>
+        <v>2.42</v>
       </c>
       <c r="M40" t="n">
-        <v>3.29</v>
+        <v>3.47</v>
       </c>
       <c r="N40" t="n">
-        <v>3.64</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,22 +5664,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M41" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N41" t="n">
-        <v>2.73</v>
+        <v>3.51</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N42" t="n">
-        <v>2.11</v>
+        <v>2.73</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.42</v>
+        <v>1.98</v>
       </c>
       <c r="M43" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N44" t="n">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="M45" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N45" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>1.84</v>
       </c>
       <c r="M47" t="n">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="N47" t="n">
-        <v>3.36</v>
+        <v>3.81</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.94</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,22 +6825,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,16 +6900,16 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
-        <v>3.51</v>
+        <v>3.91</v>
       </c>
       <c r="N51" t="n">
-        <v>3.63</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.86</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7164,10 +7164,10 @@
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7422,10 +7422,10 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>3.51</v>
       </c>
       <c r="N55" t="n">
-        <v>4.15</v>
+        <v>3.63</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="Z55" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8055,10 +8055,10 @@
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X59" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X60" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>1.92</v>
+        <v>2.63</v>
       </c>
       <c r="M65" t="n">
-        <v>3.45</v>
+        <v>3.11</v>
       </c>
       <c r="N65" t="n">
-        <v>3.7</v>
+        <v>2.39</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M66" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N66" t="n">
         <v>3.4</v>
-      </c>
-      <c r="M66" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N66" t="n">
-        <v>2.2</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8967,7 +8967,7 @@
         <v>2.35</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="M67" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>1.9</v>
+        <v>2.55</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="M68" t="n">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>2.39</v>
+        <v>3.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z69" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="M70" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="N70" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.52</v>
+        <v>1.64</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.4</v>
+        <v>3.55</v>
       </c>
       <c r="M74" t="n">
-        <v>3.15</v>
+        <v>3.21</v>
       </c>
       <c r="N74" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N75" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N76" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="M79" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N79" t="n">
-        <v>3.63</v>
+        <v>4.8</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,49 +10731,49 @@
         </is>
       </c>
       <c r="L80" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M80" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N80" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0</v>
+      </c>
+      <c r="S80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" t="n">
+        <v>0</v>
+      </c>
+      <c r="W80" t="n">
+        <v>0</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z80" t="n">
         <v>1.95</v>
-      </c>
-      <c r="M80" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="N80" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>0</v>
-      </c>
-      <c r="S80" t="n">
-        <v>0</v>
-      </c>
-      <c r="T80" t="n">
-        <v>0</v>
-      </c>
-      <c r="U80" t="n">
-        <v>0</v>
-      </c>
-      <c r="V80" t="n">
-        <v>0</v>
-      </c>
-      <c r="W80" t="n">
-        <v>0</v>
-      </c>
-      <c r="X80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>1.77</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.24</v>
+        <v>2.67</v>
       </c>
       <c r="M82" t="n">
-        <v>3.03</v>
+        <v>3.35</v>
       </c>
       <c r="N82" t="n">
-        <v>2.91</v>
+        <v>2.52</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.25</v>
+        <v>1.72</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M88" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,49 +11892,49 @@
         </is>
       </c>
       <c r="L89" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="M89" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="N89" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" t="n">
+        <v>0</v>
+      </c>
+      <c r="U89" t="n">
+        <v>0</v>
+      </c>
+      <c r="V89" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" t="n">
+        <v>0</v>
+      </c>
+      <c r="X89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y89" t="n">
         <v>2.25</v>
       </c>
-      <c r="M89" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N89" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0</v>
-      </c>
-      <c r="S89" t="n">
-        <v>0</v>
-      </c>
-      <c r="T89" t="n">
-        <v>0</v>
-      </c>
-      <c r="U89" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" t="n">
-        <v>0</v>
-      </c>
-      <c r="W89" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y89" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z89" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.22</v>
+        <v>1.95</v>
       </c>
       <c r="M91" t="n">
-        <v>6.3</v>
+        <v>3.28</v>
       </c>
       <c r="N91" t="n">
-        <v>9.5</v>
+        <v>3.3</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="M92" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="N92" t="n">
-        <v>4.8</v>
+        <v>9.5</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,16 +12318,16 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB92" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z95" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="M99" t="n">
-        <v>3.37</v>
+        <v>3.45</v>
       </c>
       <c r="N99" t="n">
-        <v>2.54</v>
+        <v>2.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13608,10 +13608,10 @@
         <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
       <c r="M104" t="n">
-        <v>5.2</v>
+        <v>3.7</v>
       </c>
       <c r="N104" t="n">
-        <v>8.4</v>
+        <v>4.8</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="M105" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N105" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M106" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N106" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>6.8</v>
+        <v>1.85</v>
       </c>
       <c r="M107" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="N107" t="n">
-        <v>1.5</v>
+        <v>3.75</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z107" t="n">
         <v>1.95</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>1.85</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="N108" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14376,16 +14376,16 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X108" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="M109" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="N109" t="n">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M110" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N110" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z110" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.98</v>
+        <v>6.8</v>
       </c>
       <c r="M111" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="N111" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="M112" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="N112" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="M113" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N113" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="M114" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="N114" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="M116" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="N116" t="n">
-        <v>6.7</v>
+        <v>4.05</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z116" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>2.35</v>
+        <v>4</v>
       </c>
       <c r="M117" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N117" t="n">
-        <v>3.15</v>
+        <v>1.77</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>2.15</v>
+        <v>1.68</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,7 +15597,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -15607,12 +15607,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.65</v>
+        <v>2.64</v>
       </c>
       <c r="M118" t="n">
-        <v>3.7</v>
+        <v>2.89</v>
       </c>
       <c r="N118" t="n">
-        <v>4.8</v>
+        <v>2.9</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15666,16 +15666,16 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X118" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="M119" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="N119" t="n">
-        <v>1.77</v>
+        <v>8.4</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="M120" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N120" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Z120" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,7 +16188,7 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z122" t="n">
         <v>1.8</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N123" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,7 +16317,7 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Z123" t="n">
         <v>1.8</v>
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M132" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z132" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,10 +1224,10 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
@@ -1278,22 +1278,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="M7" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,13 +1443,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1482,10 +1482,10 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Spartak Moskva</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Krylya Sovetov</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.6</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>2.55</v>
+        <v>4.5</v>
       </c>
       <c r="N12" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Krasnodar</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>Zenit</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="M13" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6.5</v>
+        <v>2.6</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2346,13 +2346,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="M16" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Baltika</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Rostov</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -3084,22 +3084,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="M30" t="n">
-        <v>3.23</v>
+        <v>3.05</v>
       </c>
       <c r="N30" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.04</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="M32" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="N32" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="O32" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>3.17</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N40" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.75</v>
+        <v>2.42</v>
       </c>
       <c r="M41" t="n">
-        <v>3.8</v>
+        <v>3.47</v>
       </c>
       <c r="N41" t="n">
-        <v>3.51</v>
+        <v>2.4</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,16 +5739,16 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N42" t="n">
-        <v>2.73</v>
+        <v>1.48</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="N43" t="n">
-        <v>3.17</v>
+        <v>3.51</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6051,22 +6051,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N44" t="n">
-        <v>2.11</v>
+        <v>2.73</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="M45" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="N45" t="n">
-        <v>3.64</v>
+        <v>2.11</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.9</v>
+        <v>2.02</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="M54" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N54" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,16 +7416,16 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M56" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M58" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,10 +7932,10 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M66" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N66" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.65</v>
+        <v>3.55</v>
       </c>
       <c r="M69" t="n">
-        <v>3</v>
+        <v>3.21</v>
       </c>
       <c r="N69" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="M70" t="n">
-        <v>3.05</v>
+        <v>3.11</v>
       </c>
       <c r="N70" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="M71" t="n">
-        <v>3.15</v>
+        <v>3.5</v>
       </c>
       <c r="N71" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9695,17 +9695,17 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="M74" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N74" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="M76" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N76" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>2.01</v>
+        <v>1.6</v>
       </c>
       <c r="M78" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="N78" t="n">
-        <v>3.57</v>
+        <v>4.8</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>2.05</v>
+        <v>1.55</v>
       </c>
       <c r="Z78" t="n">
-        <v>1.77</v>
+        <v>2.3</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.67</v>
+        <v>2.24</v>
       </c>
       <c r="M82" t="n">
-        <v>3.35</v>
+        <v>3.03</v>
       </c>
       <c r="N82" t="n">
-        <v>2.52</v>
+        <v>2.91</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.03</v>
+        <v>1.65</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M86" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N86" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z87" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,49 +11763,49 @@
         </is>
       </c>
       <c r="L88" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M88" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N88" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z88" t="n">
         <v>1.77</v>
-      </c>
-      <c r="M88" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N88" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
-      <c r="R88" t="n">
-        <v>0</v>
-      </c>
-      <c r="S88" t="n">
-        <v>0</v>
-      </c>
-      <c r="T88" t="n">
-        <v>0</v>
-      </c>
-      <c r="U88" t="n">
-        <v>0</v>
-      </c>
-      <c r="V88" t="n">
-        <v>0</v>
-      </c>
-      <c r="W88" t="n">
-        <v>0</v>
-      </c>
-      <c r="X88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y88" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z88" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.95</v>
+        <v>1.19</v>
       </c>
       <c r="M91" t="n">
-        <v>3.28</v>
+        <v>6</v>
       </c>
       <c r="N91" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,16 +12189,16 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB91" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1.22</v>
+        <v>2.67</v>
       </c>
       <c r="M92" t="n">
-        <v>6.3</v>
+        <v>3.35</v>
       </c>
       <c r="N92" t="n">
-        <v>9.5</v>
+        <v>2.52</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,16 +12318,16 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z92" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA92" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB92" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>0</v>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M94" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M98" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N98" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="M99" t="n">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="N99" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M101" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N103" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="M104" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N104" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.77</v>
+        <v>1.55</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="M105" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N105" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>1.45</v>
+        <v>2.08</v>
       </c>
       <c r="M106" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="N106" t="n">
-        <v>6.7</v>
+        <v>3.35</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,10 +14124,10 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AA106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M107" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="M108" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N108" t="n">
-        <v>4.7</v>
+        <v>4.05</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M109" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="N109" t="n">
-        <v>4.5</v>
+        <v>3.89</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.71</v>
+        <v>6.8</v>
       </c>
       <c r="M110" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N110" t="n">
-        <v>3.89</v>
+        <v>1.5</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="Z110" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>6.8</v>
+        <v>2.64</v>
       </c>
       <c r="M111" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="N111" t="n">
-        <v>1.5</v>
+        <v>2.9</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X111" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.85</v>
+        <v>1.66</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M112" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="N112" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M113" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>2.35</v>
+        <v>1.7</v>
       </c>
       <c r="M114" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="N114" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15210,22 +15210,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,49 +15375,49 @@
         </is>
       </c>
       <c r="L116" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N116" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0</v>
+      </c>
+      <c r="S116" t="n">
+        <v>0</v>
+      </c>
+      <c r="T116" t="n">
+        <v>0</v>
+      </c>
+      <c r="U116" t="n">
+        <v>0</v>
+      </c>
+      <c r="V116" t="n">
+        <v>0</v>
+      </c>
+      <c r="W116" t="n">
+        <v>0</v>
+      </c>
+      <c r="X116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z116" t="n">
         <v>1.7</v>
-      </c>
-      <c r="M116" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="N116" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
-      <c r="R116" t="n">
-        <v>0</v>
-      </c>
-      <c r="S116" t="n">
-        <v>0</v>
-      </c>
-      <c r="T116" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" t="n">
-        <v>0</v>
-      </c>
-      <c r="V116" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y116" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z116" t="n">
-        <v>1.93</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,7 +15468,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -15478,12 +15478,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>4</v>
+        <v>1.73</v>
       </c>
       <c r="M117" t="n">
         <v>3.75</v>
       </c>
       <c r="N117" t="n">
-        <v>1.77</v>
+        <v>4.8</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>2.64</v>
+        <v>4.3</v>
       </c>
       <c r="M118" t="n">
-        <v>2.89</v>
+        <v>3.74</v>
       </c>
       <c r="N118" t="n">
-        <v>2.9</v>
+        <v>1.62</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15666,22 +15666,22 @@
         <v>0</v>
       </c>
       <c r="W118" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.23</v>
+        <v>1.68</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AA118" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB118" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15726,7 +15726,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15762,13 +15762,13 @@
         </is>
       </c>
       <c r="L119" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M119" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N119" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="O119" t="n">
         <v>0</v>
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="M120" t="n">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="N120" t="n">
-        <v>4.8</v>
+        <v>3.68</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16887,7 +16887,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -16923,13 +16923,13 @@
         </is>
       </c>
       <c r="L128" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M128" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N128" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O128" t="n">
         <v>0</v>
@@ -16962,10 +16962,10 @@
         <v>0</v>
       </c>
       <c r="Y128" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Z128" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AA128" t="n">
         <v>0</v>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M129" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z129" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M131" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z131" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N132" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17826,13 +17826,13 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M135" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N135" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O135" t="n">
         <v>0</v>
@@ -17865,10 +17865,10 @@
         <v>0</v>
       </c>
       <c r="Y135" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z135" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA135" t="n">
         <v>0</v>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK135"/>
+  <dimension ref="A1:AK134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="M2" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4.05</v>
+        <v>3.35</v>
       </c>
       <c r="N5" t="n">
-        <v>4.05</v>
+        <v>5.1</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.2</v>
+        <v>1.58</v>
       </c>
       <c r="M6" t="n">
-        <v>3.85</v>
+        <v>3.61</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,13 +1314,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>3.81</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1353,10 +1353,10 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Malaysia Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Terengganu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Melaka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45919.375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="9">
@@ -1536,22 +1536,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Malaysia Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Terengganu</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Melaka</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,16 +1639,16 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45919.41666666666</v>
@@ -1660,27 +1660,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,19 +1768,19 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Spartak Moskva</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Krylya Sovetov</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>5.25</v>
       </c>
       <c r="M12" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N12" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Krasnodar</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Zenit</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2305,12 +2305,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="AK15" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="16">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>2.55</v>
+        <v>3.11</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Baltika</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rostov</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2643,10 +2643,10 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
@@ -2683,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="AK17" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="18">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2812,7 +2812,7 @@
         <v>0</v>
       </c>
       <c r="AK18" s="3" t="n">
-        <v>45919.47916666666</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="19">
@@ -2821,27 +2821,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2865,10 +2865,10 @@
         <v>2.48</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="N19" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.65</v>
+        <v>2.04</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AK19" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="20">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="AK20" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="21">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,22 +3471,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.51041666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.23</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.46</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,10 +4578,10 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45919.51041666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="34">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.52430555555</v>
       </c>
     </row>
     <row r="36">
@@ -5014,12 +5014,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5134,7 +5134,7 @@
         <v>0</v>
       </c>
       <c r="AK36" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="37">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5263,7 +5263,7 @@
         <v>0</v>
       </c>
       <c r="AK37" s="3" t="n">
-        <v>45919.52430555555</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="38">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.9</v>
+        <v>1.47</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="M40" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>3.51</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.42</v>
+        <v>1.85</v>
       </c>
       <c r="M41" t="n">
-        <v>3.47</v>
+        <v>3.29</v>
       </c>
       <c r="N41" t="n">
-        <v>2.4</v>
+        <v>3.64</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="M42" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N42" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,10 +5868,10 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA42" t="n">
         <v>0</v>
@@ -5922,22 +5922,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="M43" t="n">
-        <v>3.8</v>
+        <v>3.34</v>
       </c>
       <c r="N43" t="n">
-        <v>3.51</v>
+        <v>2.73</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,16 +6126,16 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.88</v>
+        <v>2.09</v>
       </c>
       <c r="M45" t="n">
-        <v>3.35</v>
+        <v>3.39</v>
       </c>
       <c r="N45" t="n">
-        <v>2.11</v>
+        <v>3.36</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="47">
@@ -6438,22 +6438,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6567,22 +6567,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="M48" t="n">
-        <v>3.39</v>
+        <v>3.35</v>
       </c>
       <c r="N48" t="n">
-        <v>3.36</v>
+        <v>1.9</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6645,7 +6645,7 @@
         <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6820,27 +6820,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,16 +6894,16 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="AK50" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="51">
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="M54" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="N54" t="n">
-        <v>4.15</v>
+        <v>5.1</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.54</v>
+        <v>1.79</v>
       </c>
       <c r="M56" t="n">
-        <v>4.1</v>
+        <v>3.51</v>
       </c>
       <c r="N56" t="n">
-        <v>4.4</v>
+        <v>3.63</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,16 +7674,16 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC56" t="n">
         <v>0</v>
@@ -7728,22 +7728,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N57" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7803,10 +7803,10 @@
         <v>0</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
         <v>0</v>
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="M58" t="n">
-        <v>3.51</v>
+        <v>4.1</v>
       </c>
       <c r="N58" t="n">
-        <v>3.63</v>
+        <v>4.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N60" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8184,10 +8184,10 @@
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y60" t="n">
         <v>0</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N62" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.59375</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45919.59375</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8792,17 +8792,17 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>1.92</v>
+        <v>2.85</v>
       </c>
       <c r="M66" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>3.7</v>
+        <v>2.55</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.68</v>
+        <v>1.58</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,7 +9179,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>3.55</v>
+        <v>2.1</v>
       </c>
       <c r="M69" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="N69" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="M70" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="N70" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>1.93</v>
+        <v>3.55</v>
       </c>
       <c r="M71" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="N71" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N72" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z72" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9792,22 +9792,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M74" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N74" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="M75" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="N75" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.35</v>
+        <v>1.72</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="M76" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N76" t="n">
-        <v>2.9</v>
+        <v>4.8</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,17 +10254,17 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.12</v>
+        <v>1.55</v>
       </c>
       <c r="Z76" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB76" t="n">
         <v>1.64</v>
       </c>
-      <c r="AA76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>0</v>
-      </c>
       <c r="AC76" t="n">
         <v>0</v>
       </c>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="77">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10473,13 +10473,13 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -10512,10 +10512,10 @@
         <v>0</v>
       </c>
       <c r="Y78" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z78" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA78" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N79" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10647,10 +10647,10 @@
         <v>0</v>
       </c>
       <c r="AA79" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB79" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M80" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,10 +10770,10 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M82" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,10 +11157,10 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z85" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M86" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="N86" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z86" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,49 +11634,49 @@
         </is>
       </c>
       <c r="L87" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="M87" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="N87" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z87" t="n">
         <v>1.77</v>
-      </c>
-      <c r="M87" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N87" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="O87" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="n">
-        <v>0</v>
-      </c>
-      <c r="T87" t="n">
-        <v>0</v>
-      </c>
-      <c r="U87" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" t="n">
-        <v>0</v>
-      </c>
-      <c r="W87" t="n">
-        <v>0</v>
-      </c>
-      <c r="X87" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y87" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z87" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.95</v>
+        <v>2.24</v>
       </c>
       <c r="M88" t="n">
-        <v>3.28</v>
+        <v>3.03</v>
       </c>
       <c r="N88" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M89" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="M90" t="n">
-        <v>3.35</v>
+        <v>3.61</v>
       </c>
       <c r="N90" t="n">
-        <v>3.63</v>
+        <v>3.59</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12109,12 +12109,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M91" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N91" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12195,10 +12195,10 @@
         <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
       <c r="AK91" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="92">
@@ -12238,12 +12238,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.67</v>
+        <v>2.17</v>
       </c>
       <c r="M92" t="n">
-        <v>3.35</v>
+        <v>3.47</v>
       </c>
       <c r="N92" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12358,7 +12358,7 @@
         <v>0</v>
       </c>
       <c r="AK92" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="93">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.64</v>
+        <v>1.84</v>
       </c>
       <c r="M94" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N94" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.67</v>
+        <v>2.35</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Jagiellonia Białystok</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,13 +12795,13 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="M96" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="O96" t="n">
         <v>0</v>
@@ -12834,10 +12834,10 @@
         <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z96" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA96" t="n">
         <v>0</v>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z97" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="M98" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Jagiellonia Białystok</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>3.37</v>
+        <v>0</v>
       </c>
       <c r="N99" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13221,10 +13221,10 @@
         <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M100" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N100" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.06</v>
+        <v>1.64</v>
       </c>
       <c r="M101" t="n">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="N101" t="n">
-        <v>2.9</v>
+        <v>4.6</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.89</v>
+        <v>1.67</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.81</v>
+        <v>2.1</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13528,12 +13528,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M102" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X102" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y102" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13648,7 +13648,7 @@
         <v>0</v>
       </c>
       <c r="AK102" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="103">
@@ -13657,27 +13657,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="M103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13777,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="AK103" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="104">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="M104" t="n">
-        <v>3.25</v>
+        <v>3.72</v>
       </c>
       <c r="N104" t="n">
-        <v>4.2</v>
+        <v>3.92</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.4</v>
+        <v>1.54</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.55</v>
+        <v>2.33</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="M105" t="n">
-        <v>3.72</v>
+        <v>3.04</v>
       </c>
       <c r="N105" t="n">
-        <v>3.92</v>
+        <v>2.94</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="Z105" t="n">
-        <v>2.33</v>
+        <v>1.7</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2.08</v>
+        <v>4.3</v>
       </c>
       <c r="M106" t="n">
-        <v>3.35</v>
+        <v>3.74</v>
       </c>
       <c r="N106" t="n">
-        <v>3.35</v>
+        <v>1.62</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="Z106" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M107" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="M108" t="n">
-        <v>4.1</v>
+        <v>3.41</v>
       </c>
       <c r="N108" t="n">
-        <v>4.05</v>
+        <v>4.4</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.71</v>
+        <v>1.3</v>
       </c>
       <c r="M109" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="N109" t="n">
-        <v>3.89</v>
+        <v>7.1</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>6.8</v>
+        <v>1.82</v>
       </c>
       <c r="M110" t="n">
-        <v>4.2</v>
+        <v>3.34</v>
       </c>
       <c r="N110" t="n">
-        <v>1.5</v>
+        <v>3.68</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>2.64</v>
+        <v>5.6</v>
       </c>
       <c r="M111" t="n">
-        <v>2.89</v>
+        <v>3.78</v>
       </c>
       <c r="N111" t="n">
-        <v>2.9</v>
+        <v>1.48</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14763,16 +14763,16 @@
         <v>0</v>
       </c>
       <c r="W111" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.23</v>
+        <v>1.89</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,7 +14823,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N112" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Z112" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.32</v>
+        <v>1.7</v>
       </c>
       <c r="M113" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="N113" t="n">
-        <v>8.4</v>
+        <v>4.05</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z113" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="M115" t="n">
-        <v>4.7</v>
+        <v>3.04</v>
       </c>
       <c r="N115" t="n">
-        <v>6.7</v>
+        <v>3.86</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="Z115" t="n">
-        <v>2.2</v>
+        <v>1.55</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.35</v>
+        <v>2.08</v>
       </c>
       <c r="M116" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N116" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="M117" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N117" t="n">
-        <v>4.8</v>
+        <v>3.89</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Z117" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="M118" t="n">
-        <v>3.74</v>
+        <v>5.2</v>
       </c>
       <c r="N118" t="n">
-        <v>1.62</v>
+        <v>8.4</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,16 +15672,16 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AA118" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB118" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
         <v>0</v>
@@ -15721,12 +15721,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -15736,12 +15736,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="120">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="M120" t="n">
-        <v>3.34</v>
+        <v>3.05</v>
       </c>
       <c r="N120" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>1.78</v>
+        <v>2.3</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="121">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16113,7 +16113,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -16123,12 +16123,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.99</v>
+        <v>1.77</v>
       </c>
       <c r="M122" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N122" t="n">
-        <v>3.64</v>
+        <v>4.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16237,12 +16237,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.67708333334</v>
       </c>
     </row>
     <row r="124">
@@ -16366,12 +16366,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Villarreal II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N124" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z124" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45919.67708333334</v>
+        <v>45919.6875</v>
       </c>
     </row>
     <row r="125">
@@ -16495,27 +16495,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45919.6875</v>
+        <v>45919.79166666666</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N126" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z126" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,7 +16744,7 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45919.79166666666</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -16758,7 +16758,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16794,13 +16794,13 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="M127" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O127" t="n">
         <v>0</v>
@@ -16833,10 +16833,10 @@
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Z127" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AA127" t="n">
         <v>0</v>
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17011,12 +17011,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="M129" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N129" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="O129" t="n">
         <v>0</v>
@@ -17091,10 +17091,10 @@
         <v>0</v>
       </c>
       <c r="Y129" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AA129" t="n">
         <v>0</v>
@@ -17131,7 +17131,7 @@
         <v>0</v>
       </c>
       <c r="AK129" s="3" t="n">
-        <v>45919.83333333334</v>
+        <v>45919.85416666666</v>
       </c>
     </row>
     <row r="130">
@@ -17140,12 +17140,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -17155,12 +17155,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>2.55</v>
+        <v>1.55</v>
       </c>
       <c r="M130" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="N130" t="n">
-        <v>2.55</v>
+        <v>5.3</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -17220,10 +17220,10 @@
         <v>0</v>
       </c>
       <c r="Y130" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Z130" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="AA130" t="n">
         <v>0</v>
@@ -17260,7 +17260,7 @@
         <v>0</v>
       </c>
       <c r="AK130" s="3" t="n">
-        <v>45919.85416666666</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="131">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="M131" t="n">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="N131" t="n">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17349,10 +17349,10 @@
         <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17398,12 +17398,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Houston Dash</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17439,13 +17439,13 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M132" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N132" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O132" t="n">
         <v>0</v>
@@ -17478,10 +17478,10 @@
         <v>0</v>
       </c>
       <c r="Y132" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z132" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AA132" t="n">
         <v>0</v>
@@ -17518,7 +17518,7 @@
         <v>0</v>
       </c>
       <c r="AK132" s="3" t="n">
-        <v>45919.875</v>
+        <v>45919.89583333334</v>
       </c>
     </row>
     <row r="133">
@@ -17527,12 +17527,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M133" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O133" t="n">
         <v>0</v>
@@ -17607,10 +17607,10 @@
         <v>0</v>
       </c>
       <c r="Y133" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA133" t="n">
         <v>0</v>
@@ -17647,7 +17647,7 @@
         <v>0</v>
       </c>
       <c r="AK133" s="3" t="n">
-        <v>45919.89583333334</v>
+        <v>45919.95833333334</v>
       </c>
     </row>
     <row r="134">
@@ -17776,135 +17776,6 @@
         <v>0</v>
       </c>
       <c r="AK134" s="3" t="n">
-        <v>45919.95833333334</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L135" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M135" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N135" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O135" t="n">
-        <v>0</v>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK134"/>
+  <dimension ref="A1:AK126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,52 +678,52 @@
         <v>3.45</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Z2" t="n">
         <v>1.72</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Singapore S.League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hougang United</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Geylang International</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45919.35416666666</v>
+        <v>45919.375</v>
       </c>
     </row>
     <row r="4">
@@ -891,22 +891,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="M4" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.35</v>
+        <v>1.92</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.68</v>
+        <v>2.58</v>
       </c>
       <c r="M7" t="n">
-        <v>3.82</v>
+        <v>3.15</v>
       </c>
       <c r="N7" t="n">
-        <v>3.81</v>
+        <v>2.53</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45919.375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="8">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="15">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="17">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,61 +3249,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
@@ -3316,10 +3316,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
         <v>0</v>
@@ -3342,22 +3342,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3636,13 +3636,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3675,10 +3675,10 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3804,10 +3804,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -3858,22 +3858,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4240,27 +4240,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45919.51041666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>5.1</v>
+        <v>1.75</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>1.6</v>
+        <v>3.51</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4578,16 +4578,16 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,13 +4926,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4965,10 +4965,10 @@
         <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45919.52430555555</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="36">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>3.17</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="M37" t="n">
-        <v>4.1</v>
+        <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>1.48</v>
+        <v>2.73</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.98</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.34</v>
+        <v>4.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.17</v>
+        <v>1.48</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5530,12 +5530,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5616,10 +5616,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.42</v>
+        <v>1.84</v>
       </c>
       <c r="M42" t="n">
-        <v>3.47</v>
+        <v>3.78</v>
       </c>
       <c r="N42" t="n">
-        <v>2.4</v>
+        <v>3.81</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,16 +5868,16 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="43">
@@ -5917,27 +5917,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="M43" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="N43" t="n">
-        <v>2.73</v>
+        <v>3.36</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,16 +5997,16 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="45">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.09</v>
+        <v>1.86</v>
       </c>
       <c r="M45" t="n">
-        <v>3.39</v>
+        <v>3.1</v>
       </c>
       <c r="N45" t="n">
-        <v>3.36</v>
+        <v>4</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6249,16 +6249,16 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.57291666666</v>
       </c>
     </row>
     <row r="46">
@@ -6304,27 +6304,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="47">
@@ -6433,27 +6433,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.35</v>
+        <v>3.91</v>
       </c>
       <c r="N48" t="n">
-        <v>1.9</v>
+        <v>5.1</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6696,22 +6696,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="M50" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="N50" t="n">
-        <v>6.4</v>
+        <v>4.15</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6894,16 +6894,16 @@
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6954,22 +6954,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="M51" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N51" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="M52" t="n">
-        <v>3.17</v>
+        <v>3.3</v>
       </c>
       <c r="N52" t="n">
-        <v>3.04</v>
+        <v>6.4</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7152,16 +7152,16 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,13 +7248,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7287,10 +7287,10 @@
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
         <v>0</v>
@@ -7341,22 +7341,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>3.91</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,22 +7470,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,22 +7599,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.79</v>
+        <v>1.58</v>
       </c>
       <c r="M56" t="n">
-        <v>3.51</v>
+        <v>3.7</v>
       </c>
       <c r="N56" t="n">
-        <v>3.63</v>
+        <v>5.6</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,22 +7857,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.54</v>
+        <v>2.35</v>
       </c>
       <c r="M58" t="n">
-        <v>4.1</v>
+        <v>3.17</v>
       </c>
       <c r="N58" t="n">
-        <v>4.4</v>
+        <v>3.04</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7932,16 +7932,16 @@
         <v>0</v>
       </c>
       <c r="Y58" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
@@ -7981,12 +7981,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M59" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M61" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="62">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="M62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45919.59375</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="63">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8534,17 +8534,17 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="M64" t="n">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="N64" t="n">
-        <v>2.39</v>
+        <v>2.9</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M65" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N65" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9179,17 +9179,17 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="M68" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.1</v>
+        <v>2.63</v>
       </c>
       <c r="M69" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="N69" t="n">
-        <v>3.4</v>
+        <v>2.39</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>3.55</v>
+        <v>2.67</v>
       </c>
       <c r="M71" t="n">
-        <v>3.21</v>
+        <v>3.35</v>
       </c>
       <c r="N71" t="n">
-        <v>1.9</v>
+        <v>2.52</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="Z71" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="72">
@@ -9658,27 +9658,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N72" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9738,10 +9738,10 @@
         <v>0</v>
       </c>
       <c r="Y72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z73" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -9996,10 +9996,10 @@
         <v>0</v>
       </c>
       <c r="Y74" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z74" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA74" t="n">
         <v>0</v>
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.625</v>
       </c>
     </row>
     <row r="75">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="M75" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="N75" t="n">
-        <v>2.52</v>
+        <v>3.3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="Z75" t="n">
-        <v>2.03</v>
+        <v>1.77</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Lommel United</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>1.6</v>
+        <v>2.01</v>
       </c>
       <c r="M76" t="n">
-        <v>4.1</v>
+        <v>2.92</v>
       </c>
       <c r="N76" t="n">
-        <v>4.8</v>
+        <v>3.57</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,16 +10254,16 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="AA76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.19</v>
+        <v>1.77</v>
       </c>
       <c r="M79" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N79" t="n">
-        <v>8.6</v>
+        <v>3.59</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,16 +10641,16 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z79" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA79" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB79" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>4.4</v>
+        <v>1.19</v>
       </c>
       <c r="M80" t="n">
-        <v>3.8</v>
+        <v>6</v>
       </c>
       <c r="N80" t="n">
-        <v>1.7</v>
+        <v>8.6</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB80" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC80" t="n">
         <v>0</v>
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RWDM</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="M82" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z82" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,13 +11118,13 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="M83" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="N83" t="n">
-        <v>3.63</v>
+        <v>4.8</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -11157,16 +11157,16 @@
         <v>0</v>
       </c>
       <c r="Y83" t="n">
-        <v>1.82</v>
+        <v>1.55</v>
       </c>
       <c r="Z83" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11247,13 +11247,13 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M84" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -11286,10 +11286,10 @@
         <v>0</v>
       </c>
       <c r="Y84" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z84" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA84" t="n">
         <v>0</v>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="M85" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11415,10 +11415,10 @@
         <v>0</v>
       </c>
       <c r="Y85" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z85" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA85" t="n">
         <v>0</v>
@@ -11464,12 +11464,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11584,7 +11584,7 @@
         <v>0</v>
       </c>
       <c r="AK86" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="87">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Città di Campobasso</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11634,13 +11634,13 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O87" t="n">
         <v>0</v>
@@ -11673,10 +11673,10 @@
         <v>0</v>
       </c>
       <c r="Y87" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z87" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA87" t="n">
         <v>0</v>
@@ -11713,7 +11713,7 @@
         <v>0</v>
       </c>
       <c r="AK87" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="88">
@@ -11722,12 +11722,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Forlì</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z88" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11842,7 +11842,7 @@
         <v>0</v>
       </c>
       <c r="AK88" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="89">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.01</v>
+        <v>1.84</v>
       </c>
       <c r="M89" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="N89" t="n">
-        <v>3.57</v>
+        <v>4.4</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11931,10 +11931,10 @@
         <v>0</v>
       </c>
       <c r="Y89" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z89" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AA89" t="n">
         <v>0</v>
@@ -11971,7 +11971,7 @@
         <v>0</v>
       </c>
       <c r="AK89" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="90">
@@ -11980,12 +11980,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,13 +12021,13 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="M90" t="n">
-        <v>3.61</v>
+        <v>3.45</v>
       </c>
       <c r="N90" t="n">
-        <v>3.59</v>
+        <v>2.9</v>
       </c>
       <c r="O90" t="n">
         <v>0</v>
@@ -12060,10 +12060,10 @@
         <v>0</v>
       </c>
       <c r="Y90" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Z90" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AA90" t="n">
         <v>0</v>
@@ -12100,7 +12100,7 @@
         <v>0</v>
       </c>
       <c r="AK90" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.64583333334</v>
       </c>
     </row>
     <row r="91">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Città di Campobasso</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,13 +12150,13 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O91" t="n">
         <v>0</v>
@@ -12189,10 +12189,10 @@
         <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA91" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12279,13 +12279,13 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -12318,10 +12318,10 @@
         <v>0</v>
       </c>
       <c r="Y92" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z92" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AA92" t="n">
         <v>0</v>
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N94" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,13 +12666,13 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="M95" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -12705,10 +12705,10 @@
         <v>0</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z95" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AA95" t="n">
         <v>0</v>
@@ -12883,27 +12883,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Forlì</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,16 +12963,16 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA97" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB97" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC97" t="n">
         <v>0</v>
@@ -13003,7 +13003,7 @@
         <v>0</v>
       </c>
       <c r="AK97" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="98">
@@ -13012,12 +13012,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>FCV Dender EH</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,13 +13053,13 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>2.06</v>
+        <v>1.71</v>
       </c>
       <c r="M98" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="N98" t="n">
-        <v>2.9</v>
+        <v>3.89</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -13092,10 +13092,10 @@
         <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.81</v>
+        <v>2.3</v>
       </c>
       <c r="AA98" t="n">
         <v>0</v>
@@ -13132,7 +13132,7 @@
         <v>0</v>
       </c>
       <c r="AK98" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="99">
@@ -13141,12 +13141,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13182,13 +13182,13 @@
         </is>
       </c>
       <c r="L99" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="M99" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O99" t="n">
         <v>0</v>
@@ -13215,16 +13215,16 @@
         <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA99" t="n">
         <v>0</v>
@@ -13261,7 +13261,7 @@
         <v>0</v>
       </c>
       <c r="AK99" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="100">
@@ -13270,27 +13270,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M100" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="O100" t="n">
         <v>0</v>
@@ -13350,10 +13350,10 @@
         <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA100" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>0</v>
       </c>
       <c r="AK100" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="101">
@@ -13399,27 +13399,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,13 +13440,13 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>1.64</v>
+        <v>2.22</v>
       </c>
       <c r="M101" t="n">
-        <v>4.1</v>
+        <v>3.04</v>
       </c>
       <c r="N101" t="n">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -13479,10 +13479,10 @@
         <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="Z101" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="AA101" t="n">
         <v>0</v>
@@ -13519,7 +13519,7 @@
         <v>0</v>
       </c>
       <c r="AK101" s="3" t="n">
-        <v>45919.64583333334</v>
+        <v>45919.65625</v>
       </c>
     </row>
     <row r="102">
@@ -13533,22 +13533,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13569,13 +13569,13 @@
         </is>
       </c>
       <c r="L102" t="n">
-        <v>2.64</v>
+        <v>1.67</v>
       </c>
       <c r="M102" t="n">
-        <v>2.89</v>
+        <v>3.41</v>
       </c>
       <c r="N102" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="O102" t="n">
         <v>0</v>
@@ -13602,16 +13602,16 @@
         <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Z102" t="n">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AA102" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="M103" t="n">
-        <v>3.5</v>
+        <v>3.04</v>
       </c>
       <c r="N103" t="n">
-        <v>4.1</v>
+        <v>3.86</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.97</v>
+        <v>2.4</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,22 +13791,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Bala Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Briton Ferry</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M104" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.22</v>
+        <v>1.82</v>
       </c>
       <c r="M105" t="n">
-        <v>3.04</v>
+        <v>3.34</v>
       </c>
       <c r="N105" t="n">
-        <v>2.94</v>
+        <v>3.68</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14049,22 +14049,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Wales Welsh Premier League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Cardiff MU</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>The New Saints</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14085,13 +14085,13 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="N106" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O106" t="n">
         <v>0</v>
@@ -14124,16 +14124,16 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA106" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AB106" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>0</v>
@@ -14178,22 +14178,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="M107" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="N107" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,22 +14307,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Olympique Lyonnais</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,49 +14343,49 @@
         </is>
       </c>
       <c r="L108" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M108" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0</v>
+      </c>
+      <c r="S108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
+        <v>0</v>
+      </c>
+      <c r="U108" t="n">
+        <v>0</v>
+      </c>
+      <c r="V108" t="n">
+        <v>0</v>
+      </c>
+      <c r="W108" t="n">
+        <v>0</v>
+      </c>
+      <c r="X108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y108" t="n">
         <v>1.67</v>
       </c>
-      <c r="M108" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N108" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0</v>
-      </c>
-      <c r="S108" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" t="n">
-        <v>0</v>
-      </c>
-      <c r="V108" t="n">
-        <v>0</v>
-      </c>
-      <c r="W108" t="n">
-        <v>0</v>
-      </c>
-      <c r="X108" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y108" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z108" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14472,13 +14472,13 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="M109" t="n">
-        <v>4.7</v>
+        <v>3.78</v>
       </c>
       <c r="N109" t="n">
-        <v>7.1</v>
+        <v>1.48</v>
       </c>
       <c r="O109" t="n">
         <v>0</v>
@@ -14511,10 +14511,10 @@
         <v>0</v>
       </c>
       <c r="Y109" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="Z109" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AA109" t="n">
         <v>0</v>
@@ -14565,22 +14565,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,13 +14601,13 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>1.82</v>
+        <v>2.08</v>
       </c>
       <c r="M110" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="N110" t="n">
-        <v>3.68</v>
+        <v>3.35</v>
       </c>
       <c r="O110" t="n">
         <v>0</v>
@@ -14640,10 +14640,10 @@
         <v>0</v>
       </c>
       <c r="Y110" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AA110" t="n">
         <v>0</v>
@@ -14694,22 +14694,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Portadown</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,13 +14730,13 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>5.6</v>
+        <v>1.7</v>
       </c>
       <c r="M111" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="N111" t="n">
-        <v>1.48</v>
+        <v>4.05</v>
       </c>
       <c r="O111" t="n">
         <v>0</v>
@@ -14769,10 +14769,10 @@
         <v>0</v>
       </c>
       <c r="Y111" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AA111" t="n">
         <v>0</v>
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Cardiff MU</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>The New Saints</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14859,13 +14859,13 @@
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M112" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O112" t="n">
         <v>0</v>
@@ -14898,10 +14898,10 @@
         <v>0</v>
       </c>
       <c r="Y112" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z112" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AA112" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -14962,12 +14962,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Portadown</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,13 +14988,13 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="M113" t="n">
-        <v>4.1</v>
+        <v>3.41</v>
       </c>
       <c r="N113" t="n">
-        <v>4.05</v>
+        <v>3.64</v>
       </c>
       <c r="O113" t="n">
         <v>0</v>
@@ -15027,10 +15027,10 @@
         <v>0</v>
       </c>
       <c r="Y113" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="AA113" t="n">
         <v>0</v>
@@ -15067,7 +15067,7 @@
         <v>0</v>
       </c>
       <c r="AK113" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -15076,12 +15076,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wales Welsh Premier League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Bala Town</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Briton Ferry</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15196,7 +15196,7 @@
         <v>0</v>
       </c>
       <c r="AK114" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="115">
@@ -15205,27 +15205,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="M115" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="N115" t="n">
-        <v>3.86</v>
+        <v>3.5</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>
@@ -15325,7 +15325,7 @@
         <v>0</v>
       </c>
       <c r="AK115" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -15334,12 +15334,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Rio Ave FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,13 +15375,13 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.08</v>
+        <v>7.8</v>
       </c>
       <c r="M116" t="n">
-        <v>3.35</v>
+        <v>5.1</v>
       </c>
       <c r="N116" t="n">
-        <v>3.35</v>
+        <v>1.37</v>
       </c>
       <c r="O116" t="n">
         <v>0</v>
@@ -15414,10 +15414,10 @@
         <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.72</v>
+        <v>2.25</v>
       </c>
       <c r="AA116" t="n">
         <v>0</v>
@@ -15454,7 +15454,7 @@
         <v>0</v>
       </c>
       <c r="AK116" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.67708333334</v>
       </c>
     </row>
     <row r="117">
@@ -15463,27 +15463,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FCV Dender EH</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15504,13 +15504,13 @@
         </is>
       </c>
       <c r="L117" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="M117" t="n">
-        <v>3.6</v>
+        <v>3.09</v>
       </c>
       <c r="N117" t="n">
-        <v>3.89</v>
+        <v>4.5</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="Z117" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AA117" t="n">
         <v>0</v>
@@ -15583,7 +15583,7 @@
         <v>0</v>
       </c>
       <c r="AK117" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.79166666666</v>
       </c>
     </row>
     <row r="118">
@@ -15592,27 +15592,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Olympique Lyonnais</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>1.32</v>
+        <v>3.2</v>
       </c>
       <c r="M118" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="N118" t="n">
-        <v>8.4</v>
+        <v>2.08</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="Z118" t="n">
-        <v>2.2</v>
+        <v>1.82</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15712,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="AK118" s="3" t="n">
-        <v>45919.65625</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="119">
@@ -15721,27 +15721,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15801,10 +15801,10 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA119" t="n">
         <v>0</v>
@@ -15841,7 +15841,7 @@
         <v>0</v>
       </c>
       <c r="AK119" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -15850,27 +15850,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15891,13 +15891,13 @@
         </is>
       </c>
       <c r="L120" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M120" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O120" t="n">
         <v>0</v>
@@ -15930,10 +15930,10 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z120" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA120" t="n">
         <v>0</v>
@@ -15970,7 +15970,7 @@
         <v>0</v>
       </c>
       <c r="AK120" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.83333333334</v>
       </c>
     </row>
     <row r="121">
@@ -15979,27 +15979,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>New York City</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlotte</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="M121" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="N121" t="n">
-        <v>3.64</v>
+        <v>2.55</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16099,7 +16099,7 @@
         <v>0</v>
       </c>
       <c r="AK121" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -16108,27 +16108,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Houston Dash</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16149,13 +16149,13 @@
         </is>
       </c>
       <c r="L122" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="M122" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N122" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="O122" t="n">
         <v>0</v>
@@ -16188,10 +16188,10 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Z122" t="n">
-        <v>1.87</v>
+        <v>1.73</v>
       </c>
       <c r="AA122" t="n">
         <v>0</v>
@@ -16228,7 +16228,7 @@
         <v>0</v>
       </c>
       <c r="AK122" s="3" t="n">
-        <v>45919.66666666666</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="123">
@@ -16237,27 +16237,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rio Ave FC</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16278,13 +16278,13 @@
         </is>
       </c>
       <c r="L123" t="n">
-        <v>7.8</v>
+        <v>1.55</v>
       </c>
       <c r="M123" t="n">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="N123" t="n">
-        <v>1.37</v>
+        <v>5.3</v>
       </c>
       <c r="O123" t="n">
         <v>0</v>
@@ -16317,10 +16317,10 @@
         <v>0</v>
       </c>
       <c r="Y123" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="Z123" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="AA123" t="n">
         <v>0</v>
@@ -16357,7 +16357,7 @@
         <v>0</v>
       </c>
       <c r="AK123" s="3" t="n">
-        <v>45919.67708333334</v>
+        <v>45919.875</v>
       </c>
     </row>
     <row r="124">
@@ -16366,27 +16366,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Villarreal II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="AK124" s="3" t="n">
-        <v>45919.6875</v>
+        <v>45919.89583333334</v>
       </c>
     </row>
     <row r="125">
@@ -16495,12 +16495,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16536,13 +16536,13 @@
         </is>
       </c>
       <c r="L125" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M125" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="N125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O125" t="n">
         <v>0</v>
@@ -16575,10 +16575,10 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z125" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AA125" t="n">
         <v>0</v>
@@ -16615,7 +16615,7 @@
         <v>0</v>
       </c>
       <c r="AK125" s="3" t="n">
-        <v>45919.79166666666</v>
+        <v>45919.95833333334</v>
       </c>
     </row>
     <row r="126">
@@ -16624,12 +16624,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16665,13 +16665,13 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O126" t="n">
         <v>0</v>
@@ -16704,10 +16704,10 @@
         <v>0</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA126" t="n">
         <v>0</v>
@@ -16744,1038 +16744,6 @@
         <v>0</v>
       </c>
       <c r="AK126" s="3" t="n">
-        <v>45919.83333333334</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Miami FC II</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="G127" t="n">
-        <v>0</v>
-      </c>
-      <c r="H127" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" t="n">
-        <v>0</v>
-      </c>
-      <c r="J127" t="n">
-        <v>0</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L127" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="M127" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N127" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="O127" t="n">
-        <v>0</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0</v>
-      </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" s="3" t="n">
-        <v>45919.83333333334</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Sporting KC II</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Whitecaps II</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0</v>
-      </c>
-      <c r="N128" t="n">
-        <v>0</v>
-      </c>
-      <c r="O128" t="n">
-        <v>0</v>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" s="3" t="n">
-        <v>45919.83333333334</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>New York City</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Charlotte</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L129" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="M129" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N129" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O129" t="n">
-        <v>0</v>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" s="3" t="n">
-        <v>45919.85416666666</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Orlando Pride</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>North Carolina Courage</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L130" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M130" t="n">
-        <v>4</v>
-      </c>
-      <c r="N130" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O130" t="n">
-        <v>0</v>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK130" s="3" t="n">
-        <v>45919.875</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Houston Dash</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L131" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M131" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N131" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="O131" t="n">
-        <v>0</v>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK131" s="3" t="n">
-        <v>45919.875</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Austin II</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>St. Louis City II</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" s="3" t="n">
-        <v>45919.89583333334</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Racing Louisville</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L133" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="M133" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N133" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O133" t="n">
-        <v>0</v>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" s="3" t="n">
-        <v>45919.95833333334</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>45919</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>USA MLS Next Pro</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Los Angeles II</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Real Monarchs</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0</v>
-      </c>
-      <c r="N134" t="n">
-        <v>0</v>
-      </c>
-      <c r="O134" t="n">
-        <v>0</v>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK134" s="3" t="n">
         <v>45919.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-09-19.xlsx
+++ b/jogos_2025-09-19.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK126"/>
+  <dimension ref="A1:AK136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -708,7 +708,7 @@
         <v>2.97</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="Z2" t="n">
         <v>1.72</v>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Singapore S.League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hougang United</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Geylang International</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45919.375</v>
+        <v>45919.35416666666</v>
       </c>
     </row>
     <row r="4">
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malut United</t>
+          <t>Port FC</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Madura United</t>
+          <t>Chonburi</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="M4" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
-        <v>3.81</v>
+        <v>4.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.78</v>
+        <v>1.42</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.92</v>
+        <v>2.49</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Persebaya Surabaya</t>
+          <t>Malut United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Semen Padang</t>
+          <t>Madura United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="M5" t="n">
-        <v>3.35</v>
+        <v>3.82</v>
       </c>
       <c r="N5" t="n">
-        <v>5.1</v>
+        <v>3.81</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1095,10 +1095,10 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Port FC</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chonburi</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.61</v>
+        <v>3.85</v>
       </c>
       <c r="N6" t="n">
-        <v>3.57</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
@@ -1252,10 +1252,10 @@
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1273,27 +1273,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Persebaya Surabaya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Semen Padang</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1310,65 +1310,65 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.58</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>2.53</v>
+        <v>5.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45919.41666666666</v>
+        <v>45919.375</v>
       </c>
     </row>
     <row r="8">
@@ -1531,27 +1531,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Dhafra</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,65 +1568,65 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
@@ -1639,19 +1639,19 @@
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45919.4375</v>
+        <v>45919.41666666666</v>
       </c>
     </row>
     <row r="10">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>İstanbulspor</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Çorum Belediyespor</t>
+          <t>Al Dhafra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1780,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
-        <v>45919.45833333334</v>
+        <v>45919.4375</v>
       </c>
     </row>
     <row r="11">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.6</v>
+        <v>5.25</v>
       </c>
       <c r="M11" t="n">
-        <v>2.55</v>
+        <v>4.33</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1863,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>5.25</v>
+        <v>2.56</v>
       </c>
       <c r="M12" t="n">
-        <v>4.33</v>
+        <v>2.47</v>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>3.33</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ümraniyespor</t>
+          <t>İstanbulspor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>76 Iğdır Belediyespor</t>
+          <t>Çorum Belediyespor</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2176,12 +2176,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Ümraniyespor</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>76 Iğdır Belediyespor</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,10 +2284,10 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="3" t="n">
-        <v>45919.48958333334</v>
+        <v>45919.45833333334</v>
       </c>
     </row>
     <row r="15">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2514,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="AK16" s="3" t="n">
-        <v>45919.5</v>
+        <v>45919.48958333334</v>
       </c>
     </row>
     <row r="17">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Karvan FK</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chadormalu SC</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>İnter Bakı</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,22 +2826,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haka</t>
+          <t>Qabala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2901,10 +2901,10 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sumqayıt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,61 +3120,61 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
@@ -3187,10 +3187,10 @@
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3213,22 +3213,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sumqayıt</t>
+          <t>Haka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Qabala</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Turan</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Turan</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,61 +3507,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
@@ -3574,10 +3574,10 @@
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3600,22 +3600,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karvan FK</t>
+          <t>Shortan</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="M26" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>5.2</v>
+        <v>4.79</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shortan</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Bunyodkor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Chadormalu SC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bunyodkor</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>İnter Bakı</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="AK30" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.5</v>
       </c>
     </row>
     <row r="31">
@@ -4369,12 +4369,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Malavan</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,61 +4410,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>7.06</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
@@ -4477,10 +4477,10 @@
         </is>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI31" t="n">
         <v>0</v>
@@ -4489,7 +4489,7 @@
         <v>0</v>
       </c>
       <c r="AK31" s="3" t="n">
-        <v>45919.52083333334</v>
+        <v>45919.51041666666</v>
       </c>
     </row>
     <row r="32">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SV Stripfing Weiden</t>
+          <t>Malavan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,13 +4539,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4584,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4618,7 +4618,7 @@
         <v>0</v>
       </c>
       <c r="AK32" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="33">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>GKS Katowice</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,13 +4668,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4707,10 +4707,10 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -4747,7 +4747,7 @@
         <v>0</v>
       </c>
       <c r="AK33" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="34">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,13 +4797,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.88</v>
+        <v>5.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.11</v>
+        <v>1.6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4836,10 +4836,10 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="AK34" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52083333334</v>
       </c>
     </row>
     <row r="35">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Y35" t="n">
         <v>1.8</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>0</v>
       </c>
       <c r="AK35" s="3" t="n">
-        <v>45919.54166666666</v>
+        <v>45919.52430555555</v>
       </c>
     </row>
     <row r="36">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,13 +5055,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="M36" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5094,10 +5094,10 @@
         <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.92</v>
+        <v>1.47</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>KTP</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="M37" t="n">
         <v>3.34</v>
       </c>
       <c r="N37" t="n">
-        <v>2.73</v>
+        <v>3.17</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,13 +5313,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.64</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5352,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>GKS Katowice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>2.42</v>
       </c>
       <c r="M39" t="n">
-        <v>4.1</v>
+        <v>3.47</v>
       </c>
       <c r="N39" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5481,10 +5481,10 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
@@ -5530,27 +5530,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bani Yas</t>
+          <t>KTP</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Jazira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5571,13 +5571,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5610,16 +5610,16 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>0</v>
       </c>
       <c r="AK40" s="3" t="n">
-        <v>45919.55208333334</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="41">
@@ -5659,27 +5659,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5739,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA41" t="n">
         <v>0</v>
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="AK41" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="42">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>SV Stripfing Weiden</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5829,13 +5829,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="M42" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="N42" t="n">
-        <v>3.81</v>
+        <v>3.51</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -5868,13 +5868,13 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AB42" t="n">
         <v>1.62</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="AK42" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="43">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preußen Münster</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -5958,13 +5958,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.09</v>
+        <v>5</v>
       </c>
       <c r="M43" t="n">
-        <v>3.39</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.36</v>
+        <v>1.48</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -5997,10 +5997,10 @@
         <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Z43" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AA43" t="n">
         <v>0</v>
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="AK43" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.54166666666</v>
       </c>
     </row>
     <row r="44">
@@ -6046,27 +6046,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Bani Yas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Al Jazira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6166,7 +6166,7 @@
         <v>0</v>
       </c>
       <c r="AK44" s="3" t="n">
-        <v>45919.5625</v>
+        <v>45919.55208333334</v>
       </c>
     </row>
     <row r="45">
@@ -6175,27 +6175,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6249,10 +6249,10 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
         <v>0</v>
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="AK45" s="3" t="n">
-        <v>45919.57291666666</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="46">
@@ -6304,12 +6304,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Linköping</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6345,13 +6345,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6384,10 +6384,10 @@
         <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
         <v>0</v>
@@ -6424,7 +6424,7 @@
         <v>0</v>
       </c>
       <c r="AK46" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="47">
@@ -6433,12 +6433,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Arminia Bielefeld</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,13 +6474,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6513,16 +6513,16 @@
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>0</v>
       </c>
       <c r="AK47" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="48">
@@ -6562,27 +6562,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Kaiserslautern</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Preußen Münster</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>1.5</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>3.91</v>
+        <v>3.39</v>
       </c>
       <c r="N48" t="n">
-        <v>5.1</v>
+        <v>3.36</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="Z48" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6682,7 +6682,7 @@
         <v>0</v>
       </c>
       <c r="AK48" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.5625</v>
       </c>
     </row>
     <row r="49">
@@ -6691,27 +6691,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="M49" t="n">
-        <v>3.51</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>3.63</v>
+        <v>4.1</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6765,16 +6765,16 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -6811,7 +6811,7 @@
         <v>0</v>
       </c>
       <c r="AK49" s="3" t="n">
-        <v>45919.58333333334</v>
+        <v>45919.57291666666</v>
       </c>
     </row>
     <row r="50">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fredericia</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6861,13 +6861,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="M50" t="n">
-        <v>4</v>
+        <v>3.17</v>
       </c>
       <c r="N50" t="n">
-        <v>4.15</v>
+        <v>3.04</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -6900,10 +6900,10 @@
         <v>0</v>
       </c>
       <c r="Y50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z50" t="n">
         <v>1.65</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>2.25</v>
       </c>
       <c r="AA50" t="n">
         <v>0</v>
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="M51" t="n">
-        <v>4.1</v>
+        <v>3.91</v>
       </c>
       <c r="N51" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,16 +7029,16 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Smouha SC</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7152,16 +7152,16 @@
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,22 +7212,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Linköping</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Foolad</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Fredericia</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="M55" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Al Ahly</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ceramica Cleopatra</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Foolad</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Smouha SC</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="M58" t="n">
-        <v>3.17</v>
+        <v>2.84</v>
       </c>
       <c r="N58" t="n">
-        <v>3.04</v>
+        <v>6.4</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
@@ -7926,16 +7926,16 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X58" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y58" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Z58" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AA58" t="n">
         <v>0</v>
@@ -7981,27 +7981,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>3.4</v>
+        <v>1.54</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="N59" t="n">
-        <v>2.2</v>
+        <v>4.4</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,16 +8061,16 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC59" t="n">
         <v>0</v>
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="AK59" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="60">
@@ -8110,27 +8110,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>B68</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8230,7 +8230,7 @@
         <v>0</v>
       </c>
       <c r="AK60" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="61">
@@ -8239,12 +8239,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Al Ahly</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Ceramica Cleopatra</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8280,13 +8280,13 @@
         </is>
       </c>
       <c r="L61" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M61" t="n">
         <v>3.55</v>
       </c>
-      <c r="M61" t="n">
-        <v>3.21</v>
-      </c>
       <c r="N61" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="O61" t="n">
         <v>0</v>
@@ -8319,10 +8319,10 @@
         <v>0</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z61" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA61" t="n">
         <v>0</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="AK61" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="62">
@@ -8368,27 +8368,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,13 +8409,13 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="M62" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="N62" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="O62" t="n">
         <v>0</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.2</v>
+        <v>1.86</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AA62" t="n">
         <v>0</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
       <c r="AK62" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="63">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L63" t="n">
@@ -8617,7 +8617,7 @@
         <v>0</v>
       </c>
       <c r="AK63" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.58333333334</v>
       </c>
     </row>
     <row r="64">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,13 +8667,13 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N64" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O64" t="n">
         <v>0</v>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="Y64" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AA64" t="n">
         <v>0</v>
@@ -8746,7 +8746,7 @@
         <v>0</v>
       </c>
       <c r="AK64" s="3" t="n">
-        <v>45919.60416666666</v>
+        <v>45919.59375</v>
       </c>
     </row>
     <row r="65">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bourg-en-Bresse</t>
+          <t>Caen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Quevilly Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8796,13 +8796,13 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="M65" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="N65" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O65" t="n">
         <v>0</v>
@@ -8835,10 +8835,10 @@
         <v>0</v>
       </c>
       <c r="Y65" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="Z65" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="AA65" t="n">
         <v>0</v>
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stade Briochin</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Orléans</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -8925,13 +8925,13 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.85</v>
+        <v>2.65</v>
       </c>
       <c r="M66" t="n">
         <v>3</v>
       </c>
       <c r="N66" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8964,10 +8964,10 @@
         <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="Z66" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="AA66" t="n">
         <v>0</v>
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Bourg-en-Bresse</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Orléans</t>
+          <t>Quevilly Rouen</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.65</v>
+        <v>2.1</v>
       </c>
       <c r="M67" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N67" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.18</v>
+        <v>2.35</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Caen</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9183,13 +9183,13 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="M68" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N68" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O68" t="n">
         <v>0</v>
@@ -9222,10 +9222,10 @@
         <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Z68" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA68" t="n">
         <v>0</v>
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>B68</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9312,13 +9312,13 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="N69" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="O69" t="n">
         <v>0</v>
@@ -9351,10 +9351,10 @@
         <v>0</v>
       </c>
       <c r="Y69" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z69" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA69" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="L70" t="n">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9570,13 +9570,13 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="M71" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="N71" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="O71" t="n">
         <v>0</v>
@@ -9609,10 +9609,10 @@
         <v>0</v>
       </c>
       <c r="Y71" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="Z71" t="n">
-        <v>2.03</v>
+        <v>1.64</v>
       </c>
       <c r="AA71" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>0</v>
       </c>
       <c r="AK71" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="72">
@@ -9658,12 +9658,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Stade Briochin</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,49 +9699,49 @@
         </is>
       </c>
       <c r="L72" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="M72" t="n">
+        <v>3</v>
+      </c>
+      <c r="N72" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
+      </c>
+      <c r="V72" t="n">
+        <v>0</v>
+      </c>
+      <c r="W72" t="n">
+        <v>0</v>
+      </c>
+      <c r="X72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="n">
         <v>2.25</v>
       </c>
-      <c r="M72" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N72" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O72" t="n">
-        <v>0</v>
-      </c>
-      <c r="P72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
-      <c r="R72" t="n">
-        <v>0</v>
-      </c>
-      <c r="S72" t="n">
-        <v>0</v>
-      </c>
-      <c r="T72" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" t="n">
-        <v>0</v>
-      </c>
-      <c r="V72" t="n">
-        <v>0</v>
-      </c>
-      <c r="W72" t="n">
-        <v>0</v>
-      </c>
-      <c r="X72" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y72" t="n">
-        <v>1.95</v>
-      </c>
       <c r="Z72" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AA72" t="n">
         <v>0</v>
@@ -9778,7 +9778,7 @@
         <v>0</v>
       </c>
       <c r="AK72" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="73">
@@ -9787,12 +9787,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9867,10 +9867,10 @@
         <v>0</v>
       </c>
       <c r="Y73" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z73" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA73" t="n">
         <v>0</v>
@@ -9907,7 +9907,7 @@
         <v>0</v>
       </c>
       <c r="AK73" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="74">
@@ -9916,12 +9916,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10036,7 +10036,7 @@
         <v>0</v>
       </c>
       <c r="AK74" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="75">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="M75" t="n">
-        <v>3.28</v>
+        <v>3.11</v>
       </c>
       <c r="N75" t="n">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="Z75" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="AK75" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="76">
@@ -10174,12 +10174,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.01</v>
+        <v>3.4</v>
       </c>
       <c r="M76" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="N76" t="n">
-        <v>3.57</v>
+        <v>2.2</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>2.05</v>
+        <v>2.35</v>
       </c>
       <c r="Z76" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10294,7 +10294,7 @@
         <v>0</v>
       </c>
       <c r="AK76" s="3" t="n">
-        <v>45919.625</v>
+        <v>45919.60416666666</v>
       </c>
     </row>
     <row r="77">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10383,10 +10383,10 @@
         <v>0</v>
       </c>
       <c r="Y77" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z77" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA77" t="n">
         <v>0</v>
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>3.59</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10641,10 +10641,10 @@
         <v>0</v>
       </c>
       <c r="Y79" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z79" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA79" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,13 +10860,13 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O81" t="n">
         <v>0</v>
@@ -10899,10 +10899,10 @@
         <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA81" t="n">
         <v>0</v>
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Lommel United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RWDM</t>
+          <t